--- a/Hospital_Qswift_App_E2E_Appium_Test_Report.xlsx
+++ b/Hospital_Qswift_App_E2E_Appium_Test_Report.xlsx
@@ -62,7 +62,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>28/10/2026, 9:17:25 pm</t>
+    <t>29/10/2026, 12:09:08 am</t>
   </si>
   <si>
     <t>Total Mobile Test Cases</t>
